--- a/SK네트웍스 Family AI 캠프 31기curriculum.xlsx
+++ b/SK네트웍스 Family AI 캠프 31기curriculum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Playdata\SKN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Playdata\SKN\SKN31\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DAA8D46-B138-4F60-95D0-7E1AA30C6EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F463FF-238E-4318-87B4-A47E23AC2109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve"> 2일자 개강 및 확정자 신고 이후 변경 신고 필요
@@ -52,6 +53,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>25.02.03
@@ -268,7 +270,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy&quot;년 &quot;mmmm&quot; &quot;d&quot;일 &quot;dddd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,6 +402,13 @@
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -566,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -684,6 +693,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4110,7 +4122,9 @@
         <v>38</v>
       </c>
       <c r="E98" s="12"/>
-      <c r="F98" s="1"/>
+      <c r="F98" s="43">
+        <v>0.8</v>
+      </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -25903,7 +25917,7 @@
     <col min="1" max="29" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:29" ht="14.4">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -25971,7 +25985,7 @@
       <c r="AB2" s="13"/>
       <c r="AC2" s="13"/>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:29" ht="14.4">
       <c r="A3" s="13"/>
       <c r="B3" s="15" t="s">
         <v>42</v>
@@ -26044,7 +26058,7 @@
       <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:29" ht="14.4">
       <c r="A4" s="13"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -26099,7 +26113,7 @@
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:29" ht="14.4">
       <c r="A5" s="13"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -26136,7 +26150,7 @@
       <c r="AB5" s="13"/>
       <c r="AC5" s="13"/>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:29" ht="14.4">
       <c r="A6" s="13"/>
       <c r="B6" s="26">
         <v>5</v>
@@ -26209,7 +26223,7 @@
       <c r="AB6" s="13"/>
       <c r="AC6" s="13"/>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:29" ht="14.4">
       <c r="A7" s="13"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -26242,7 +26256,7 @@
       <c r="AB7" s="13"/>
       <c r="AC7" s="13"/>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:29" ht="14.4">
       <c r="A8" s="13"/>
       <c r="B8" s="26">
         <v>12</v>
@@ -26315,7 +26329,7 @@
       <c r="AB8" s="13"/>
       <c r="AC8" s="13"/>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9" spans="1:29" ht="14.4">
       <c r="A9" s="13"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -26348,7 +26362,7 @@
       <c r="AB9" s="13"/>
       <c r="AC9" s="13"/>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:29" ht="14.4">
       <c r="A10" s="13"/>
       <c r="B10" s="26">
         <v>19</v>
@@ -26421,7 +26435,7 @@
       <c r="AB10" s="13"/>
       <c r="AC10" s="13"/>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:29" ht="14.4">
       <c r="A11" s="13"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -26452,7 +26466,7 @@
       <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:29" ht="14.4">
       <c r="A12" s="13"/>
       <c r="B12" s="26">
         <v>26</v>
@@ -26513,7 +26527,7 @@
       <c r="AB12" s="13"/>
       <c r="AC12" s="13"/>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:29" ht="14.4">
       <c r="A13" s="13"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -26548,7 +26562,7 @@
       <c r="AB13" s="13"/>
       <c r="AC13" s="13"/>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:29" ht="14.4">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -26585,7 +26599,7 @@
       <c r="AB14" s="13"/>
       <c r="AC14" s="13"/>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:29" ht="14.4">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -26616,7 +26630,7 @@
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:29" ht="14.4">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -26649,7 +26663,7 @@
       <c r="AB16" s="13"/>
       <c r="AC16" s="13"/>
     </row>
-    <row r="17" spans="1:29">
+    <row r="17" spans="1:29" ht="14.4">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -26717,7 +26731,7 @@
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
     </row>
-    <row r="19" spans="1:29">
+    <row r="19" spans="1:29" ht="14.4">
       <c r="A19" s="13"/>
       <c r="B19" s="15" t="s">
         <v>42</v>
@@ -26790,7 +26804,7 @@
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
     </row>
-    <row r="20" spans="1:29">
+    <row r="20" spans="1:29" ht="14.4">
       <c r="A20" s="13"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -26841,7 +26855,7 @@
       <c r="AB20" s="13"/>
       <c r="AC20" s="13"/>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21" spans="1:29" ht="14.4">
       <c r="A21" s="13"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -26872,7 +26886,7 @@
       <c r="AB21" s="13"/>
       <c r="AC21" s="13"/>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22" spans="1:29" ht="14.4">
       <c r="A22" s="13"/>
       <c r="B22" s="26">
         <v>5</v>
@@ -26945,7 +26959,7 @@
       <c r="AB22" s="13"/>
       <c r="AC22" s="13"/>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23" spans="1:29" ht="14.4">
       <c r="A23" s="13"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -26976,7 +26990,7 @@
       <c r="AB23" s="13"/>
       <c r="AC23" s="13"/>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24" spans="1:29" ht="14.4">
       <c r="A24" s="13"/>
       <c r="B24" s="26">
         <v>12</v>
@@ -27049,7 +27063,7 @@
       <c r="AB24" s="13"/>
       <c r="AC24" s="13"/>
     </row>
-    <row r="25" spans="1:29">
+    <row r="25" spans="1:29" ht="14.4">
       <c r="A25" s="13"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -27084,7 +27098,7 @@
       <c r="AB25" s="13"/>
       <c r="AC25" s="13"/>
     </row>
-    <row r="26" spans="1:29">
+    <row r="26" spans="1:29" ht="14.4">
       <c r="A26" s="13"/>
       <c r="B26" s="26">
         <v>19</v>
@@ -27157,7 +27171,7 @@
       <c r="AB26" s="13"/>
       <c r="AC26" s="13"/>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27" spans="1:29" ht="14.4">
       <c r="A27" s="13"/>
       <c r="B27" s="16"/>
       <c r="C27" s="29"/>
